--- a/stories/arbres/ATOM-DIF.COR.003-02.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.003-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kenzo arrive au parc avec papa. L'herbe sent la pluie. Zoé arrive aussi. Zoé a des lunettes. Zoé a les cheveux tressés. Zoé porte un gilet rouge. Kenzo regarde. Un petit rire commence. Papa parle tout de suite. Papa dit : on ne va pas rire de l'apparence. Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. On joue. Kenzo hoche la tête. Il va vers Zoé. Ils prennent la corde. Ils sautent. Parce qu'on ne va pas rire, le jeu continue. Papa dit encore : on ne va pas rire de l'apparence. Kenzo tend la corde. Zoé saute. Les lunettes restent sur le nez. Le gilet rouge bouge. Ils sourient.</t>
+          <t>Kenzo arrive au parc avec papa. L'herbe sent la pluie. Zoé arrive aussi. Zoé a des lunettes. Zoé a les cheveux tressés. Zoé porte un gilet rouge. Kenzo regarde. Un petit rire commence. Papa parle tout de suite. On ne va pas rire de l'apparence. Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. On joue. Kenzo hoche la tête. Il va vers Zoé. Ils prennent la corde. Ils sautent. Parce qu'on ne va pas rire, le jeu continue. Papa dit encore : on ne va pas rire de l'apparence. Kenzo tend la corde. Zoé saute. Les lunettes restent sur le nez. Le gilet rouge bouge. Ils sourient.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo arrive au parc avec papa. L'herbe sent la pluie. Zoé arrive aussi. Zoé a des lunettes. Zoé a les cheveux tressés. Zoé porte un gilet rouge. Kenzo regarde. Un petit rire commence. Papa parle tout de suite.
+papa|On ne va pas rire de l'apparence.
+narrateur|Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. On joue. Kenzo hoche la tête. Il va vers Zoé. Ils prennent la corde. Ils sautent. Parce qu'on ne va pas rire, le jeu continue. Papa dit encore : on ne va pas rire de l'apparence. Kenzo tend la corde. Zoé saute. Les lunettes restent sur le nez. Le gilet rouge bouge. Ils sourient.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a des lunettes. Que fait-on ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a entendu papa. On ne va pas rire de l'apparence. Kenzo et Zoé ont joué.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1824,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo pose la corde. Papa verse de l'eau. Merci, dit Zoé.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1991,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2031,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.003-02.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.003-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,11 @@
 narrateur|Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. On joue. Kenzo hoche la tête. Il va vers Zoé. Ils prennent la corde. Ils sautent. Parce qu'on ne va pas rire, le jeu continue. Papa dit encore : on ne va pas rire de l'apparence. Kenzo tend la corde. Zoé saute. Les lunettes restent sur le nez. Le gilet rouge bouge. Ils sourient.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1505,7 @@
           <t>narrateur|Zoé a des lunettes. Que fait-on ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1677,7 @@
           <t>narrateur|Kenzo a entendu papa. On ne va pas rire de l'apparence. Kenzo et Zoé ont joué.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1841,7 @@
           <t>narrateur|Kenzo pose la corde. Papa verse de l'eau. Merci, dit Zoé.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1996,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2014,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2038,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2239,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-DIF.COR.003-02.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.003-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kenzo ne rit pas de l'apparence</t>
+          <t>La corde à la branche</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Victorino et Nina sautent à la corde sous la branche. On joue. On ne rit pas de l'apparence.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kenzo arrive au parc avec papa. L'herbe sent la pluie. Zoé arrive aussi. Zoé a des lunettes. Zoé a les cheveux tressés. Zoé porte un gilet rouge. Kenzo regarde. Un petit rire commence. Papa parle tout de suite. On ne va pas rire de l'apparence. Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. On joue. Kenzo hoche la tête. Il va vers Zoé. Ils prennent la corde. Ils sautent. Parce qu'on ne va pas rire, le jeu continue. Papa dit encore : on ne va pas rire de l'apparence. Kenzo tend la corde. Zoé saute. Les lunettes restent sur le nez. Le gilet rouge bouge. Ils sourient.</t>
+          <t>Un oiseau picore près de la clôture. La corde à sauter pend à une branche basse. Elle est encore un peu humide. L'herbe sent la pluie d'hier. Papa pose le sac contre le tronc. Tu as vu la corde, Victorino ? Elle pend. Oui. Elle attend. L'écorce du tronc est rugueuse. Une fourmi monte tout droit. En ce moment, Victorino est au parc avec papa. Nina arrive sur le chemin de graviers. Nina a des lunettes. Nina a les cheveux tressés. Nina porte un gilet rouge. On joue ensemble. On ne va pas rire de l'apparence. On joue. Victorino va vers Nina. Tu viens à la corde ? Oui. Papa décroche la corde. Elle sent le coton un peu froid. Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. On joue. Victorino tient un bout. Papa tient l'autre bout. Nina saute. Le gilet rouge bouge. Les lunettes restent sur le nez. Les tresses tapent doucement le dos. Bravo, Nina. Bravo, Victorino. Vous jouez ensemble. À moi ? Oui. À toi. Nina tient un bout. Papa tourne tout doux. Victorino saute. Ses chaussures font toc dans l'herbe. Encore. Encore. Chacun son tour. C'est ça. C'est du bon travail. Un rayon passe entre les feuilles. Il allume le gilet rouge. On ne rit pas des lunettes, des cheveux ou d'un habit. On joue. Ils posent la corde un moment. L'herbe est froide sous les mains. Vous voulez de l'eau ? Oui, papa. La gourde est lisse et fraîche. Nina boit. Victorino boit. On reprend la corde ? On reprend. La corde tourne encore. Ils sautent, un après l'autre. Le jeu continue.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,73 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo arrive au parc avec papa. L'herbe sent la pluie. Zoé arrive aussi. Zoé a des lunettes. Zoé a les cheveux tressés. Zoé porte un gilet rouge. Kenzo regarde. Un petit rire commence. Papa parle tout de suite.
+          <t>narrateur|Un oiseau picore près de la clôture.
+narrateur|La corde à sauter pend à une branche basse.
+narrateur|Elle est encore un peu humide.
+narrateur|L'herbe sent la pluie d'hier.
+narrateur|Papa pose le sac contre le tronc.
+papa|Tu as vu la corde, Victorino ?
+enfant-m|Elle pend.
+papa|Oui. Elle attend.
+narrateur|L'écorce du tronc est rugueuse.
+narrateur|Une fourmi monte tout droit.
+narrateur|En ce moment, Victorino est au parc avec papa.
+narrateur|Nina arrive sur le chemin de graviers.
+narrateur|Nina a des lunettes.
+narrateur|Nina a les cheveux tressés.
+narrateur|Nina porte un gilet rouge.
+papa|On joue ensemble.
 papa|On ne va pas rire de l'apparence.
-narrateur|Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. On joue. Kenzo hoche la tête. Il va vers Zoé. Ils prennent la corde. Ils sautent. Parce qu'on ne va pas rire, le jeu continue. Papa dit encore : on ne va pas rire de l'apparence. Kenzo tend la corde. Zoé saute. Les lunettes restent sur le nez. Le gilet rouge bouge. Ils sourient.</t>
+enfant-m|On joue.
+narrateur|Victorino va vers Nina.
+enfant-m|Tu viens à la corde ?
+copine|Oui.
+narrateur|Papa décroche la corde.
+narrateur|Elle sent le coton un peu froid.
+papa|Les lunettes aident à voir.
+papa|Les cheveux sont les cheveux.
+papa|L'habit tient chaud.
+papa|On joue.
+narrateur|Victorino tient un bout.
+narrateur|Papa tient l'autre bout.
+narrateur|Nina saute.
+narrateur|Le gilet rouge bouge.
+narrateur|Les lunettes restent sur le nez.
+narrateur|Les tresses tapent doucement le dos.
+papa|Bravo, Nina.
+papa|Bravo, Victorino.
+papa|Vous jouez ensemble.
+enfant-m|À moi ?
+papa|Oui. À toi.
+narrateur|Nina tient un bout.
+narrateur|Papa tourne tout doux.
+narrateur|Victorino saute.
+narrateur|Ses chaussures font toc dans l'herbe.
+copine|Encore.
+enfant-m|Encore.
+papa|Chacun son tour. C'est ça.
+papa|C'est du bon travail.
+narrateur|Un rayon passe entre les feuilles.
+narrateur|Il allume le gilet rouge.
+papa|On ne rit pas des lunettes, des cheveux ou d'un habit.
+papa|On joue.
+narrateur|Ils posent la corde un moment.
+narrateur|L'herbe est froide sous les mains.
+papa|Vous voulez de l'eau ?
+enfant-m|Oui, papa.
+narrateur|La gourde est lisse et fraîche.
+narrateur|Nina boit.
+narrateur|Victorino boit.
+papa|On reprend la corde ?
+copine|On reprend.
+narrateur|La corde tourne encore.
+narrateur|Ils sautent, un après l'autre.
+narrateur|Le jeu continue.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>enfants_parc,corde</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1417,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Zoé a des lunettes. Que fait-on ?</t>
+          <t>Nina a des lunettes. Que fait-on ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1573,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Zoé a des lunettes. Que fait-on ?</t>
+          <t>narrateur|Nina a des lunettes.
+narrateur|Que fait-on ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1602,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a entendu papa. On ne va pas rire de l'apparence. Kenzo et Zoé ont joué.</t>
+          <t>Victorino a entendu papa. On ne va pas rire de l'apparence. Victorino et Nina ont joué. Bravo, Victorino. Tu as fait du bon travail. On a sauté. Oui. Vous avez sauté ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1746,13 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a entendu papa. On ne va pas rire de l'apparence. Kenzo et Zoé ont joué.</t>
+          <t>narrateur|Victorino a entendu papa.
+narrateur|On ne va pas rire de l'apparence.
+narrateur|Victorino et Nina ont joué.
+papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+enfant-m|On a sauté.
+papa|Oui. Vous avez sauté ensemble.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1780,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Kenzo pose la corde. Papa verse de l'eau. Merci, dit Zoé.</t>
+          <t>Victorino pose la corde sur le sac. Papa verse encore un peu d'eau. Merci. Merci à vous deux. On range ? On range. L'oiseau est encore près de la clôture. Le chemin de graviers fait criss-criss.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1838,7 +1916,14 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo pose la corde. Papa verse de l'eau. Merci, dit Zoé.</t>
+          <t>narrateur|Victorino pose la corde sur le sac.
+narrateur|Papa verse encore un peu d'eau.
+copine|Merci.
+papa|Merci à vous deux.
+papa|On range ?
+enfant-m|On range.
+narrateur|L'oiseau est encore près de la clôture.
+narrateur|Le chemin de graviers fait criss-criss.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1866,7 +1951,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a sauté à la corde. Bravo. Vous avez joué ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2006,7 +2091,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a sauté à la corde.
+papa|Bravo.
+papa|Vous avez joué ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2028,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2154,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.003-02.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.003-02.xlsx
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un oiseau picore près de la clôture. La corde à sauter pend à une branche basse. Elle est encore un peu humide. L'herbe sent la pluie d'hier. Papa pose le sac contre le tronc. Tu as vu la corde, Victorino ? Elle pend. Oui. Elle attend. L'écorce du tronc est rugueuse. Une fourmi monte tout droit. En ce moment, Victorino est au parc avec papa. Nina arrive sur le chemin de graviers. Nina a des lunettes. Nina a les cheveux tressés. Nina porte un gilet rouge. On joue ensemble. On ne va pas rire de l'apparence. On joue. Victorino va vers Nina. Tu viens à la corde ? Oui. Papa décroche la corde. Elle sent le coton un peu froid. Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. On joue. Victorino tient un bout. Papa tient l'autre bout. Nina saute. Le gilet rouge bouge. Les lunettes restent sur le nez. Les tresses tapent doucement le dos. Bravo, Nina. Bravo, Victorino. Vous jouez ensemble. À moi ? Oui. À toi. Nina tient un bout. Papa tourne tout doux. Victorino saute. Ses chaussures font toc dans l'herbe. Encore. Encore. Chacun son tour. C'est ça. C'est du bon travail. Un rayon passe entre les feuilles. Il allume le gilet rouge. On ne rit pas des lunettes, des cheveux ou d'un habit. On joue. Ils posent la corde un moment. L'herbe est froide sous les mains. Vous voulez de l'eau ? Oui, papa. La gourde est lisse et fraîche. Nina boit. Victorino boit. On reprend la corde ? On reprend. La corde tourne encore. Ils sautent, un après l'autre. Le jeu continue.</t>
+          <t>Un oiseau picore près de la clôture. La corde à sauter pend à une branche basse. Elle est encore un peu humide. L'herbe sent la pluie d'hier. Papa pose le sac contre le tronc. Tu as vu la corde, Victorino ? Elle pend. Oui. Elle attend. L'écorce du tronc est rugueuse. Une fourmi monte tout droit. En ce moment, Victorino est au parc avec papa. Nina arrive sur le chemin de graviers. Nina a des lunettes. Nina a les cheveux tressés. Nina porte un gilet rouge. On joue ensemble. On ne va pas rire de l'apparence. On joue. Victorino va vers Nina. Tu viens à la corde ? Oui. Papa décroche la corde. Elle sent le coton un peu froid. Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. On joue. Victorino tient un bout. Papa tient l'autre bout. Nina saute. Le gilet rouge bouge. Les lunettes restent sur le nez. Les tresses tapent doucement le dos. Bravo, Nina. Bravo, Victorino. Vous jouez ensemble. À moi ? Oui. À toi. Nina tient un bout. Papa tourne tout doux. Victorino saute. Ses chaussures font toc dans l'herbe. Encore. Encore. Chacun son tour. C'est ça. C'est du bon travail. Un rayon passe entre les feuilles. Il allume le gilet rouge. On ne rit pas des lunettes, des cheveux ou d'un habit. On joue. Ils posent la corde un moment. L'herbe est froide sous les mains. Vous voulez de l'eau ? Oui, papa. La gourde est lisse et fraîche. Nina boit. Victorino boit. On reprend la corde ? On reprend. La corde tourne encore. Ils sautent, un après l'autre. On compte les sauts ? Un. Deux. Trois. Bravo. Vous comptez ensemble. Une pomme de pin est sous l'arbre. Elle est rêche et brune. Elle pique un peu. Oui. On la pose près du sac. Nina pose la pomme de pin. Victorino reprend la corde. Tu tiens bien. Merci. La corde tapote l'herbe. Ça fait un petit bruit mou. À moi le milieu. Oui. À toi. Puis à Victorino. Nina saute encore. Les tresses bougent. Le gilet rouge s'envole un peu. On joue. C'est ça. On joue. Le jeu continue sous la branche.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1331,7 +1331,8 @@
 narrateur|Papa pose le sac contre le tronc.
 papa|Tu as vu la corde, Victorino ?
 enfant-m|Elle pend.
-papa|Oui. Elle attend.
+papa|Oui.
+papa|Elle attend.
 narrateur|L'écorce du tronc est rugueuse.
 narrateur|Une fourmi monte tout droit.
 narrateur|En ce moment, Victorino est au parc avec papa.
@@ -1361,14 +1362,16 @@
 papa|Bravo, Victorino.
 papa|Vous jouez ensemble.
 enfant-m|À moi ?
-papa|Oui. À toi.
+papa|Oui.
+papa|À toi.
 narrateur|Nina tient un bout.
 narrateur|Papa tourne tout doux.
 narrateur|Victorino saute.
 narrateur|Ses chaussures font toc dans l'herbe.
 copine|Encore.
 enfant-m|Encore.
-papa|Chacun son tour. C'est ça.
+papa|Chacun son tour.
+papa|C'est ça.
 papa|C'est du bon travail.
 narrateur|Un rayon passe entre les feuilles.
 narrateur|Il allume le gilet rouge.
@@ -1385,7 +1388,34 @@
 copine|On reprend.
 narrateur|La corde tourne encore.
 narrateur|Ils sautent, un après l'autre.
-narrateur|Le jeu continue.</t>
+papa|On compte les sauts ?
+enfant-m|Un.
+copine|Deux.
+enfant-m|Trois.
+papa|Bravo.
+papa|Vous comptez ensemble.
+narrateur|Une pomme de pin est sous l'arbre.
+narrateur|Elle est rêche et brune.
+enfant-m|Elle pique un peu.
+papa|Oui.
+papa|On la pose près du sac.
+narrateur|Nina pose la pomme de pin.
+narrateur|Victorino reprend la corde.
+papa|Tu tiens bien.
+papa|Merci.
+narrateur|La corde tapote l'herbe.
+narrateur|Ça fait un petit bruit mou.
+copine|À moi le milieu.
+papa|Oui.
+papa|À toi.
+papa|Puis à Victorino.
+narrateur|Nina saute encore.
+narrateur|Les tresses bougent.
+narrateur|Le gilet rouge s'envole un peu.
+papa|On joue.
+papa|C'est ça.
+enfant-m|On joue.
+narrateur|Le jeu continue sous la branche.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1602,7 +1632,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorino a entendu papa. On ne va pas rire de l'apparence. Victorino et Nina ont joué. Bravo, Victorino. Tu as fait du bon travail. On a sauté. Oui. Vous avez sauté ensemble.</t>
+          <t>Victorino a entendu papa. On ne va pas rire de l'apparence. Victorino et Nina ont joué. Bravo, Victorino. Tu as fait du bon travail. On a sauté. Oui. Vous avez sauté ensemble. Tu as invité Nina. Bravo. La corde repose sur le sac. Tu as fini de sauter un moment ? Encore un peu. Encore un peu. D'accord.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1752,7 +1782,15 @@
 papa|Bravo, Victorino.
 papa|Tu as fait du bon travail.
 enfant-m|On a sauté.
-papa|Oui. Vous avez sauté ensemble.</t>
+papa|Oui.
+papa|Vous avez sauté ensemble.
+papa|Tu as invité Nina.
+papa|Bravo.
+narrateur|La corde repose sur le sac.
+papa|Tu as fini de sauter un moment ?
+enfant-m|Encore un peu.
+papa|Encore un peu.
+papa|D'accord.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -2116,7 +2154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2159,6 +2197,27 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-DIF.COR.003-02.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.003-02.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La corde à la branche</t>
+          <t>Les cinq sauts sous le pin</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Victorino et Nina sautent à la corde sous la branche. On joue. On ne rit pas de l'apparence.</t>
+          <t>Victorino veut tourner la corde pour que Nina saute cinq fois. La corde est lourde de pluie. Ils l'essuient sur le tronc. Nina saute cinq fois.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un oiseau picore près de la clôture. La corde à sauter pend à une branche basse. Elle est encore un peu humide. L'herbe sent la pluie d'hier. Papa pose le sac contre le tronc. Tu as vu la corde, Victorino ? Elle pend. Oui. Elle attend. L'écorce du tronc est rugueuse. Une fourmi monte tout droit. En ce moment, Victorino est au parc avec papa. Nina arrive sur le chemin de graviers. Nina a des lunettes. Nina a les cheveux tressés. Nina porte un gilet rouge. On joue ensemble. On ne va pas rire de l'apparence. On joue. Victorino va vers Nina. Tu viens à la corde ? Oui. Papa décroche la corde. Elle sent le coton un peu froid. Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. On joue. Victorino tient un bout. Papa tient l'autre bout. Nina saute. Le gilet rouge bouge. Les lunettes restent sur le nez. Les tresses tapent doucement le dos. Bravo, Nina. Bravo, Victorino. Vous jouez ensemble. À moi ? Oui. À toi. Nina tient un bout. Papa tourne tout doux. Victorino saute. Ses chaussures font toc dans l'herbe. Encore. Encore. Chacun son tour. C'est ça. C'est du bon travail. Un rayon passe entre les feuilles. Il allume le gilet rouge. On ne rit pas des lunettes, des cheveux ou d'un habit. On joue. Ils posent la corde un moment. L'herbe est froide sous les mains. Vous voulez de l'eau ? Oui, papa. La gourde est lisse et fraîche. Nina boit. Victorino boit. On reprend la corde ? On reprend. La corde tourne encore. Ils sautent, un après l'autre. On compte les sauts ? Un. Deux. Trois. Bravo. Vous comptez ensemble. Une pomme de pin est sous l'arbre. Elle est rêche et brune. Elle pique un peu. Oui. On la pose près du sac. Nina pose la pomme de pin. Victorino reprend la corde. Tu tiens bien. Merci. La corde tapote l'herbe. Ça fait un petit bruit mou. À moi le milieu. Oui. À toi. Puis à Victorino. Nina saute encore. Les tresses bougent. Le gilet rouge s'envole un peu. On joue. C'est ça. On joue. Le jeu continue sous la branche.</t>
+          <t>Une pomme de pin tombe dans l'herbe. Elle fait un petit toc. Le pin sent la résine. L'écorce est rugueuse sous la main. Un peu de sève brille au soleil. Papa décroche la corde. Le coton est encore froid. Une fourmi monte sur l'écorce. Tu as entendu le toc, Victorino ? La pomme de pin. Oui. Elle est tombée toute seule. En ce moment, Victorino tient un bout. La corde sent le coton humide. Je veux tourner. Nina saute cinq fois. Cinq fois sans s'arrêter ? Oui. On compte tout haut. Nina arrive sur le gravier. Le gravier fait criss-criss. Nina a des lunettes. Nina a les cheveux tressés. Elle porte un gilet rouge. On joue ensemble. Tu sautes, Nina ? Oui. Papa tient l'autre bout. La corde tourne. Elle tape l'herbe, trop lourde. Ça fait un bruit mou. Un peu de terre colle au coton. Elle ne monte pas. Elle est mouillée. On peut l'essuyer. Sur le tronc. Puis on recompte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Kenzo arrive au parc avec papa. L'herbe sent la pluie. Zoé arrive aussi. Zoé a des lunettes. Zoé a les cheveux tressés. Zoé porte un gilet rouge. Kenzo regarde. Un petit rire commence. Papa parle tout de suite. Papa dit : on ne va &lt;emphasis level="moderate"&gt;pas&lt;/emphasis&gt; rire de l'apparence. Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. On joue. Kenzo hoche la tête. Il va vers Zoé. Ils prennent la corde. Ils sautent. Parce qu'on ne va pas rire, le jeu continue. Papa dit encore : on ne va pas rire de l'apparence. Kenzo tend la corde. Zoé saute. Les lunettes restent sur le nez. Le gilet rouge bouge. Ils sourient.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une pomme de pin tombe dans l'herbe. Elle fait un petit toc. Le pin sent la résine. L'écorce est rugueuse sous la main. Un peu de sève brille au soleil. Papa décroche la corde. Le coton est encore froid. Une fourmi monte sur l'écorce. Tu as entendu le toc, Victorino ? La pomme de pin. Oui. Elle est tombée toute seule. En ce moment, Victorino tient un bout. La corde sent le coton humide. Je veux tourner. Nina saute cinq fois. Cinq fois sans s'arrêter ? Oui. On compte tout haut. Nina arrive sur le gravier. Le gravier fait criss-criss. Nina a des lunettes. Nina a les cheveux tressés. Elle porte un gilet rouge. On joue ensemble. Tu sautes, Nina ? Oui. Papa tient l'autre bout. La corde tourne. Elle tape l'herbe, trop lourde. Ça fait un bruit mou. Un peu de terre colle au coton. Elle ne monte pas. Elle est mouillée. On peut l'essuyer. Sur le tronc. Puis on recompte.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,98 +1324,43 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Un oiseau picore près de la clôture.
-narrateur|La corde à sauter pend à une branche basse.
-narrateur|Elle est encore un peu humide.
-narrateur|L'herbe sent la pluie d'hier.
-narrateur|Papa pose le sac contre le tronc.
-papa|Tu as vu la corde, Victorino ?
-enfant-m|Elle pend.
+          <t>narrateur|Une pomme de pin tombe dans l'herbe.
+narrateur|Elle fait un petit toc.
+narrateur|Le pin sent la résine.
+narrateur|L'écorce est rugueuse sous la main.
+narrateur|Un peu de sève brille au soleil.
+narrateur|Papa décroche la corde.
+narrateur|Le coton est encore froid.
+narrateur|Une fourmi monte sur l'écorce.
+papa|Tu as entendu le toc, Victorino ?
+enfant-m|La pomme de pin.
 papa|Oui.
-papa|Elle attend.
-narrateur|L'écorce du tronc est rugueuse.
-narrateur|Une fourmi monte tout droit.
-narrateur|En ce moment, Victorino est au parc avec papa.
-narrateur|Nina arrive sur le chemin de graviers.
+papa|Elle est tombée toute seule.
+narrateur|En ce moment, Victorino tient un bout.
+narrateur|La corde sent le coton humide.
+enfant-m|Je veux tourner.
+enfant-m|Nina saute cinq fois.
+papa|Cinq fois sans s'arrêter ?
+enfant-m|Oui.
+papa|On compte tout haut.
+narrateur|Nina arrive sur le gravier.
+narrateur|Le gravier fait criss-criss.
 narrateur|Nina a des lunettes.
 narrateur|Nina a les cheveux tressés.
-narrateur|Nina porte un gilet rouge.
+narrateur|Elle porte un gilet rouge.
 papa|On joue ensemble.
-papa|On ne va pas rire de l'apparence.
-enfant-m|On joue.
-narrateur|Victorino va vers Nina.
-enfant-m|Tu viens à la corde ?
+enfant-m|Tu sautes, Nina ?
 copine|Oui.
-narrateur|Papa décroche la corde.
-narrateur|Elle sent le coton un peu froid.
-papa|Les lunettes aident à voir.
-papa|Les cheveux sont les cheveux.
-papa|L'habit tient chaud.
-papa|On joue.
-narrateur|Victorino tient un bout.
 narrateur|Papa tient l'autre bout.
-narrateur|Nina saute.
-narrateur|Le gilet rouge bouge.
-narrateur|Les lunettes restent sur le nez.
-narrateur|Les tresses tapent doucement le dos.
-papa|Bravo, Nina.
-papa|Bravo, Victorino.
-papa|Vous jouez ensemble.
-enfant-m|À moi ?
-papa|Oui.
-papa|À toi.
-narrateur|Nina tient un bout.
-narrateur|Papa tourne tout doux.
-narrateur|Victorino saute.
-narrateur|Ses chaussures font toc dans l'herbe.
-copine|Encore.
-enfant-m|Encore.
-papa|Chacun son tour.
-papa|C'est ça.
-papa|C'est du bon travail.
-narrateur|Un rayon passe entre les feuilles.
-narrateur|Il allume le gilet rouge.
-papa|On ne rit pas des lunettes, des cheveux ou d'un habit.
-papa|On joue.
-narrateur|Ils posent la corde un moment.
-narrateur|L'herbe est froide sous les mains.
-papa|Vous voulez de l'eau ?
-enfant-m|Oui, papa.
-narrateur|La gourde est lisse et fraîche.
-narrateur|Nina boit.
-narrateur|Victorino boit.
-papa|On reprend la corde ?
-copine|On reprend.
-narrateur|La corde tourne encore.
-narrateur|Ils sautent, un après l'autre.
-papa|On compte les sauts ?
-enfant-m|Un.
-copine|Deux.
-enfant-m|Trois.
-papa|Bravo.
-papa|Vous comptez ensemble.
-narrateur|Une pomme de pin est sous l'arbre.
-narrateur|Elle est rêche et brune.
-enfant-m|Elle pique un peu.
-papa|Oui.
-papa|On la pose près du sac.
-narrateur|Nina pose la pomme de pin.
-narrateur|Victorino reprend la corde.
-papa|Tu tiens bien.
-papa|Merci.
-narrateur|La corde tapote l'herbe.
-narrateur|Ça fait un petit bruit mou.
-copine|À moi le milieu.
-papa|Oui.
-papa|À toi.
-papa|Puis à Victorino.
-narrateur|Nina saute encore.
-narrateur|Les tresses bougent.
-narrateur|Le gilet rouge s'envole un peu.
-papa|On joue.
-papa|C'est ça.
-enfant-m|On joue.
-narrateur|Le jeu continue sous la branche.</t>
+narrateur|La corde tourne.
+narrateur|Elle tape l'herbe, trop lourde.
+narrateur|Ça fait un bruit mou.
+narrateur|Un peu de terre colle au coton.
+enfant-m|Elle ne monte pas.
+copine|Elle est mouillée.
+papa|On peut l'essuyer.
+papa|Sur le tronc.
+papa|Puis on recompte.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1452,7 +1397,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Zoé a des lunettes. Que fait-on ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a des lunettes. Que fait-on ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1462,12 +1407,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>pas rire</t>
+          <t>jouer</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>pas rire | on joue | pas rire de l'apparence</t>
+          <t>jouer | ensemble | sauter | on joue | essuyer | pas rire</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1482,7 +1427,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>On ne va pas rire de l'apparence. Que fait-on ?</t>
+          <t>On saute ensemble. Que fait-on ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1531,7 +1476,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1607,7 +1552,6 @@
 narrateur|Que fait-on ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1632,12 +1576,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorino a entendu papa. On ne va pas rire de l'apparence. Victorino et Nina ont joué. Bravo, Victorino. Tu as fait du bon travail. On a sauté. Oui. Vous avez sauté ensemble. Tu as invité Nina. Bravo. La corde repose sur le sac. Tu as fini de sauter un moment ? Encore un peu. Encore un peu. D'accord.</t>
+          <t>Victorino va vers Nina. Ils essuient la corde. Vous frottez le coton. Merci, Victorino. Merci, Nina. Le tronc sent la résine. Un peu de sève colle aux doigts. La corde redevient plus légère. Elle est moins lourde. On reprend ? On reprend. Les lunettes aident à voir la corde. On joue. Victorino tourne tout doux. La corde siffle un tout petit peu. Nina saute une fois. Un. Encore. Tu regardes la corde, Nina.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Kenzo a entendu papa. On ne va &lt;emphasis level="moderate"&gt;pas&lt;/emphasis&gt; rire de l'apparence. Kenzo et Zoé ont joué.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino va vers Nina. Ils essuient la corde. Vous frottez le coton. Merci, Victorino. Merci, Nina. Le tronc sent la résine. Un peu de sève colle aux doigts. La corde redevient plus légère. Elle est moins lourde. On reprend ? On reprend. Les lunettes aident à voir la corde. On joue. Victorino tourne tout doux. La corde siffle un tout petit peu. Nina saute une fois. Un. Encore. Tu regardes la corde, Nina.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1700,7 +1644,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1776,24 +1720,27 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Victorino a entendu papa.
-narrateur|On ne va pas rire de l'apparence.
-narrateur|Victorino et Nina ont joué.
-papa|Bravo, Victorino.
-papa|Tu as fait du bon travail.
-enfant-m|On a sauté.
-papa|Oui.
-papa|Vous avez sauté ensemble.
-papa|Tu as invité Nina.
-papa|Bravo.
-narrateur|La corde repose sur le sac.
-papa|Tu as fini de sauter un moment ?
-enfant-m|Encore un peu.
-papa|Encore un peu.
-papa|D'accord.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Victorino va vers Nina.
+narrateur|Ils essuient la corde.
+papa|Vous frottez le coton.
+papa|Merci, Victorino.
+papa|Merci, Nina.
+narrateur|Le tronc sent la résine.
+narrateur|Un peu de sève colle aux doigts.
+narrateur|La corde redevient plus légère.
+enfant-m|Elle est moins lourde.
+enfant-m|On reprend ?
+copine|On reprend.
+papa|Les lunettes aident à voir la corde.
+papa|On joue.
+narrateur|Victorino tourne tout doux.
+narrateur|La corde siffle un tout petit peu.
+narrateur|Nina saute une fois.
+copine|Un.
+enfant-m|Encore.
+papa|Tu regardes la corde, Nina.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1818,12 +1765,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Victorino pose la corde sur le sac. Papa verse encore un peu d'eau. Merci. Merci à vous deux. On range ? On range. L'oiseau est encore près de la clôture. Le chemin de graviers fait criss-criss.</t>
+          <t>Nina saute encore. Deux. Trois. Quatre. Le gilet rouge bouge. Les tresses tapent le dos. Les lunettes restent bien. Cinq ! Cinq ! Bravo. Tu as tourné sans t'arrêter. La corde se pose dans l'herbe. On reverse les rôles ? À toi le milieu. Nina tourne à son tour. Victorino saute. Ses chaussures font toc. C'est plus facile. Oui. La corde est sèche. Un rayon passe entre les aiguilles. Il allume le gilet rouge. La fourmi est encore sur l'écorce. La pomme de pin reste dans l'herbe. On a eu nos cinq sauts. Oui. Cinq.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Kenzo pose la corde. Papa verse de l'eau. Merci, dit Zoé.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina saute encore. Deux. Trois. Quatre. Le gilet rouge bouge. Les tresses tapent le dos. Les lunettes restent bien. Cinq ! Cinq ! Bravo. Tu as tourné sans t'arrêter. La corde se pose dans l'herbe. On reverse les rôles ? À toi le milieu. Nina tourne à son tour. Victorino saute. Ses chaussures font toc. C'est plus facile. Oui. La corde est sèche. Un rayon passe entre les aiguilles. Il allume le gilet rouge. La fourmi est encore sur l'écorce. La pomme de pin reste dans l'herbe. On a eu nos cinq sauts. Oui. Cinq.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1886,7 +1833,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1954,17 +1901,35 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Victorino pose la corde sur le sac.
-narrateur|Papa verse encore un peu d'eau.
-copine|Merci.
-papa|Merci à vous deux.
-papa|On range ?
-enfant-m|On range.
-narrateur|L'oiseau est encore près de la clôture.
-narrateur|Le chemin de graviers fait criss-criss.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Nina saute encore.
+copine|Deux.
+enfant-m|Trois.
+copine|Quatre.
+narrateur|Le gilet rouge bouge.
+narrateur|Les tresses tapent le dos.
+narrateur|Les lunettes restent bien.
+copine|Cinq !
+enfant-m|Cinq !
+papa|Bravo.
+papa|Tu as tourné sans t'arrêter.
+narrateur|La corde se pose dans l'herbe.
+papa|On reverse les rôles ?
+copine|À toi le milieu.
+narrateur|Nina tourne à son tour.
+narrateur|Victorino saute.
+narrateur|Ses chaussures font toc.
+enfant-m|C'est plus facile.
+papa|Oui.
+papa|La corde est sèche.
+narrateur|Un rayon passe entre les aiguilles.
+narrateur|Il allume le gilet rouge.
+narrateur|La fourmi est encore sur l'écorce.
+narrateur|La pomme de pin reste dans l'herbe.
+papa|On a eu nos cinq sauts.
+enfant-m|Oui.
+enfant-m|Cinq.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1989,12 +1954,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a sauté à la corde. Bravo. Vous avez joué ensemble. L'histoire est finie.</t>
+          <t>La corde pend à la branche. Elle n'est plus lourde. Nina a sauté cinq fois. Oui. Vous avez joué ensemble. Le pin sent encore la résine. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La corde pend à la branche. Elle n'est plus lourde. Nina a sauté cinq fois. Oui. Vous avez joué ensemble. Le pin sent encore la résine. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2050,14 +2015,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2129,13 +2094,15 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|On a sauté à la corde.
-papa|Bravo.
+          <t>narrateur|La corde pend à la branche.
+narrateur|Elle n'est plus lourde.
+enfant-m|Nina a sauté cinq fois.
+papa|Oui.
 papa|Vous avez joué ensemble.
+narrateur|Le pin sent encore la résine.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2154,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2220,6 +2187,13 @@
       <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.003-02.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.003-02.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une pomme de pin tombe dans l'herbe. Elle fait un petit toc. Le pin sent la résine. L'écorce est rugueuse sous la main. Un peu de sève brille au soleil. Papa décroche la corde. Le coton est encore froid. Une fourmi monte sur l'écorce. Tu as entendu le toc, Victorino ? La pomme de pin. Oui. Elle est tombée toute seule. En ce moment, Victorino tient un bout. La corde sent le coton humide. Je veux tourner. Nina saute cinq fois. Cinq fois sans s'arrêter ? Oui. On compte tout haut. Nina arrive sur le gravier. Le gravier fait criss-criss. Nina a des lunettes. Nina a les cheveux tressés. Elle porte un gilet rouge. On joue ensemble. Tu sautes, Nina ? Oui. Papa tient l'autre bout. La corde tourne. Elle tape l'herbe, trop lourde. Ça fait un bruit mou. Un peu de terre colle au coton. Elle ne monte pas. Elle est mouillée. On peut l'essuyer. Sur le tronc. Puis on recompte.</t>
+          <t>Une pomme de pin tombe dans l'herbe. Elle fait un petit toc. Le pin sent la résine. L'écorce est rugueuse sous la main. Un peu de sève brille au soleil. Papa décroche la corde. Le coton est encore froid. Une fourmi monte sur l'écorce. Tu as entendu le toc, Victorino ? La pomme de pin. Oui. Elle est tombée toute seule. En ce moment, Victorino tient un bout. La corde sent le coton humide. Je veux tourner. Nina saute cinq fois. Cinq fois sans s'arrêter ? Oui. On compte tout haut. Nina arrive sur le gravier. Le gravier fait criss-criss. Nina a des lunettes. Nina a les cheveux tressés. Elle porte un gilet rouge. Nina, tu sautes au milieu. Tu sautes, Nina ? Oui. Papa tient l'autre bout. La corde tourne. Elle tape l'herbe, trop lourde. Ça fait un bruit mou. Un peu de terre colle au coton. Elle ne monte pas. Elle est mouillée. On peut l'essuyer. Sur le tronc. Puis on recompte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Une pomme de pin tombe dans l'herbe. Elle fait un petit toc. Le pin sent la résine. L'écorce est rugueuse sous la main. Un peu de sève brille au soleil. Papa décroche la corde. Le coton est encore froid. Une fourmi monte sur l'écorce. Tu as entendu le toc, Victorino ? La pomme de pin. Oui. Elle est tombée toute seule. En ce moment, Victorino tient un bout. La corde sent le coton humide. Je veux tourner. Nina saute cinq fois. Cinq fois sans s'arrêter ? Oui. On compte tout haut. Nina arrive sur le gravier. Le gravier fait criss-criss. Nina a des lunettes. Nina a les cheveux tressés. Elle porte un gilet rouge. On joue ensemble. Tu sautes, Nina ? Oui. Papa tient l'autre bout. La corde tourne. Elle tape l'herbe, trop lourde. Ça fait un bruit mou. Un peu de terre colle au coton. Elle ne monte pas. Elle est mouillée. On peut l'essuyer. Sur le tronc. Puis on recompte.</t>
+          <t>Une pomme de pin tombe dans l'herbe. Elle fait un petit toc. Le pin sent la résine. L'écorce est rugueuse sous la main. Un peu de sève brille au soleil. Papa décroche la corde. Le coton est encore froid. Une fourmi monte sur l'écorce. Tu as entendu le toc, Victorino ? La pomme de pin. Oui. Elle est tombée toute seule. En ce moment, Victorino tient un bout. La corde sent le coton humide. Je veux tourner. Nina saute cinq fois. Cinq fois sans s'arrêter ? Oui. On compte tout haut. Nina arrive sur le gravier. Le gravier fait criss-criss. Nina a des lunettes. Nina a les cheveux tressés. Elle porte un gilet rouge. Nina, tu sautes au milieu. Tu sautes, Nina ? Oui. Papa tient l'autre bout. La corde tourne. Elle tape l'herbe, trop lourde. Ça fait un bruit mou. Un peu de terre colle au coton. Elle ne monte pas. Elle est mouillée. On peut l'essuyer. Sur le tronc. Puis on recompte.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
 narrateur|Nina a des lunettes.
 narrateur|Nina a les cheveux tressés.
 narrateur|Elle porte un gilet rouge.
-papa|On joue ensemble.
+papa|Nina, tu sautes au milieu.
 enfant-m|Tu sautes, Nina ?
 copine|Oui.
 narrateur|Papa tient l'autre bout.
@@ -1576,12 +1576,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorino va vers Nina. Ils essuient la corde. Vous frottez le coton. Merci, Victorino. Merci, Nina. Le tronc sent la résine. Un peu de sève colle aux doigts. La corde redevient plus légère. Elle est moins lourde. On reprend ? On reprend. Les lunettes aident à voir la corde. On joue. Victorino tourne tout doux. La corde siffle un tout petit peu. Nina saute une fois. Un. Encore. Tu regardes la corde, Nina.</t>
+          <t>Victorino va vers Nina. Ils essuient la corde. Vous frottez le coton. Merci, Victorino. Merci, Nina. Le tronc sent la résine. Un peu de sève colle aux doigts. La corde redevient plus légère. Elle est moins lourde. On reprend ? On reprend. Nina suit la corde des yeux. On saute. Victorino tourne tout doux. La corde siffle un tout petit peu. Nina saute une fois. Un. Encore. Tu regardes la corde, Nina.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Victorino va vers Nina. Ils essuient la corde. Vous frottez le coton. Merci, Victorino. Merci, Nina. Le tronc sent la résine. Un peu de sève colle aux doigts. La corde redevient plus légère. Elle est moins lourde. On reprend ? On reprend. Les lunettes aident à voir la corde. On joue. Victorino tourne tout doux. La corde siffle un tout petit peu. Nina saute une fois. Un. Encore. Tu regardes la corde, Nina.</t>
+          <t>Victorino va vers Nina. Ils essuient la corde. Vous frottez le coton. Merci, Victorino. Merci, Nina. Le tronc sent la résine. Un peu de sève colle aux doigts. La corde redevient plus légère. Elle est moins lourde. On reprend ? On reprend. Nina suit la corde des yeux. On saute. Victorino tourne tout doux. La corde siffle un tout petit peu. Nina saute une fois. Un. Encore. Tu regardes la corde, Nina.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1731,8 +1731,8 @@
 enfant-m|Elle est moins lourde.
 enfant-m|On reprend ?
 copine|On reprend.
-papa|Les lunettes aident à voir la corde.
-papa|On joue.
+papa|Nina suit la corde des yeux.
+papa|On saute.
 narrateur|Victorino tourne tout doux.
 narrateur|La corde siffle un tout petit peu.
 narrateur|Nina saute une fois.
@@ -1954,12 +1954,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La corde pend à la branche. Elle n'est plus lourde. Nina a sauté cinq fois. Oui. Vous avez joué ensemble. Le pin sent encore la résine. L'histoire est finie.</t>
+          <t>La corde pend à la branche. Elle n'est plus lourde. Nina a sauté cinq fois. Oui. Vous avez eu vos cinq sauts. Le pin sent encore la résine. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>La corde pend à la branche. Elle n'est plus lourde. Nina a sauté cinq fois. Oui. Vous avez joué ensemble. Le pin sent encore la résine. L'histoire est finie.</t>
+          <t>La corde pend à la branche. Elle n'est plus lourde. Nina a sauté cinq fois. Oui. Vous avez eu vos cinq sauts. Le pin sent encore la résine. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2098,7 +2098,7 @@
 narrateur|Elle n'est plus lourde.
 enfant-m|Nina a sauté cinq fois.
 papa|Oui.
-papa|Vous avez joué ensemble.
+papa|Vous avez eu vos cinq sauts.
 narrateur|Le pin sent encore la résine.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -2121,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2192,6 +2192,13 @@
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-DIF.COR.003-02.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.003-02.xlsx
@@ -1954,12 +1954,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La corde pend à la branche. Elle n'est plus lourde. Nina a sauté cinq fois. Oui. Vous avez eu vos cinq sauts. Le pin sent encore la résine. L'histoire est finie.</t>
+          <t>La corde pend à la branche. Elle n'est plus lourde. Nina a sauté cinq fois. Oui. Vous avez eu vos cinq sauts. Le pin sent encore la résine.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>La corde pend à la branche. Elle n'est plus lourde. Nina a sauté cinq fois. Oui. Vous avez eu vos cinq sauts. Le pin sent encore la résine. L'histoire est finie.</t>
+          <t>La corde pend à la branche. Elle n'est plus lourde. Nina a sauté cinq fois. Oui. Vous avez eu vos cinq sauts. Le pin sent encore la résine.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2099,8 +2099,7 @@
 enfant-m|Nina a sauté cinq fois.
 papa|Oui.
 papa|Vous avez eu vos cinq sauts.
-narrateur|Le pin sent encore la résine.
-narrateur|L'histoire est finie.</t>
+narrateur|Le pin sent encore la résine.</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2199,6 +2198,13 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-DIF.COR.003-02.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.003-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>parc</t>
+          <t>parc sous le pin</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kenzo, Zoé, papa</t>
+          <t>Victorino, Nina, papa</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.003-02.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.003-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>parc sous le pin</t>
+          <t>parc sous le pin, pomme de pin, résine, écorce</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Victorino, Nina, papa</t>
+          <t>Victorino, Nina, papa, maman</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Victorino veut tourner la corde pour que Nina saute cinq fois. La corde est lourde de pluie. Ils l'essuient sur le tronc. Nina saute cinq fois.</t>
+          <t>Une goutte de résine colle au tronc. Sur l'écorce, un éclat de résine brille. Victorino veut cinq sauts, maintenant. Nina arrive. Un rire commence. Nina se tait. La corde tape l'herbe. Victorino refuse de foncer. Ils tiennent la corde, à deux. Merci vécu. Un saut trop vite. L'éclat de résine tient sur l'écorce.</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une pomme de pin tombe dans l'herbe. Elle fait un petit toc. Le pin sent la résine. L'écorce est rugueuse sous la main. Un peu de sève brille au soleil. Papa décroche la corde. Le coton est encore froid. Une fourmi monte sur l'écorce. Tu as entendu le toc, Victorino ? La pomme de pin. Oui. Elle est tombée toute seule. En ce moment, Victorino tient un bout. La corde sent le coton humide. Je veux tourner. Nina saute cinq fois. Cinq fois sans s'arrêter ? Oui. On compte tout haut. Nina arrive sur le gravier. Le gravier fait criss-criss. Nina a des lunettes. Nina a les cheveux tressés. Elle porte un gilet rouge. Nina, tu sautes au milieu. Tu sautes, Nina ? Oui. Papa tient l'autre bout. La corde tourne. Elle tape l'herbe, trop lourde. Ça fait un bruit mou. Un peu de terre colle au coton. Elle ne monte pas. Elle est mouillée. On peut l'essuyer. Sur le tronc. Puis on recompte.</t>
+          <t>Une goutte de résine colle au tronc. Elle fait un petit fil, chaud et collant. Ça colle, papa ! Tu la vois, sur l'écorce ? Oui, un petit fil. Le pin sent la résine, tout près. Sur l'écorce, un éclat de résine brille. Il brille, maman. Tu le vois, le petit point ? Oui, un petit point. Une pomme de pin roule dans l'herbe. Elle fait toc, sec et rond. J'ai entendu le toc. La pomme de pin ? Oui, papa. L'écorce est rugueuse, sous la main. Elle pique un peu. Papa décroche la corde de la branche. Le coton est froid, un peu lourd. Le coton sent la pluie, Victorino ? Il est mouillé. En ce moment, Victorino tient un bout. Il veut cinq sauts, tout de suite. Je veux tourner, maintenant ! Nina saute cinq fois. Cinq fois, sans s'arrêter ? Oui, papa. On compte tout haut ? Oui, tout haut. Nina arrive sur le gravier. Le gravier fait criss-criss, sous ses pas. Nina a des lunettes. Nina a les cheveux tressés. Elle porte un gilet rouge. Nina, tu sautes au milieu ? Tu sautes, Nina ? Oui. Papa tient l'autre bout. Victorino regarde les lunettes, trop longtemps. Un rire commence dans sa bouche. Nina ne dit rien. Le sourire de Nina disparaît. Tu vas au milieu, maintenant ! Nina recule d'un pas. Non. Oh. Victorino tourne la corde trop vite, tout seul. La corde tape l'herbe, trop lourde. Ça fait un bruit mou. Un peu de terre colle au coton. Elle ne monte pas ! Elle est mouillée. L'éclat de résine tremble, puis tient. Le sourire de Victorino disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ses épaules tombent un peu. Papa s'accroupit à la même hauteur. Tu vois Nina, Victorino ? Oui, papa. Tes mains sont collantes, Victorino ? Un peu, maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Une pomme de pin tombe dans l'herbe. Elle fait un petit toc. Le pin sent la résine. L'écorce est rugueuse sous la main. Un peu de sève brille au soleil. Papa décroche la corde. Le coton est encore froid. Une fourmi monte sur l'écorce. Tu as entendu le toc, Victorino ? La pomme de pin. Oui. Elle est tombée toute seule. En ce moment, Victorino tient un bout. La corde sent le coton humide. Je veux tourner. Nina saute cinq fois. Cinq fois sans s'arrêter ? Oui. On compte tout haut. Nina arrive sur le gravier. Le gravier fait criss-criss. Nina a des lunettes. Nina a les cheveux tressés. Elle porte un gilet rouge. Nina, tu sautes au milieu. Tu sautes, Nina ? Oui. Papa tient l'autre bout. La corde tourne. Elle tape l'herbe, trop lourde. Ça fait un bruit mou. Un peu de terre colle au coton. Elle ne monte pas. Elle est mouillée. On peut l'essuyer. Sur le tronc. Puis on recompte.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Une goutte de résine colle au tronc. Elle fait un petit fil, chaud et collant. Ça colle, papa ! Tu la vois, sur l'écorce ? Oui, un petit fil. Le pin sent la résine, tout près. Sur l'écorce, un &lt;emphasis level="moderate"&gt;éclat de résine&lt;/emphasis&gt; brille. Il brille, maman. Tu le vois, le petit point ? Oui, un petit point. Une pomme de pin roule dans l'herbe. Elle fait toc, sec et rond. J'ai entendu le toc. La pomme de pin ? Oui, papa. L'écorce est rugueuse, sous la main. Elle pique un peu. Papa décroche la corde de la branche. Le coton est froid, un peu lourd. Le coton sent la pluie, Victorino ? Il est mouillé. En ce moment, Victorino tient un bout. Il veut cinq sauts, tout de suite. Je veux tourner, maintenant ! Nina saute cinq fois. Cinq fois, sans s'arrêter ? Oui, papa. On compte tout haut ? Oui, tout haut. Nina arrive sur le gravier. Le gravier fait criss-criss, sous ses pas. Nina a des lunettes. Nina a les cheveux tressés. Elle porte un gilet rouge. Nina, tu sautes au milieu ? Tu sautes, Nina ? Oui. Papa tient l'autre bout. Victorino regarde les lunettes, trop longtemps. Un rire commence dans sa bouche. Nina ne dit rien. Le sourire de Nina disparaît. Tu vas au milieu, maintenant ! Nina recule d'un pas. Non. Oh. Victorino tourne la corde trop vite, tout seul. La corde tape l'herbe, trop lourde. Ça fait un bruit mou. Un peu de terre colle au coton. Elle ne monte pas ! Elle est mouillée. L'éclat de résine tremble, puis tient. Le sourire de Victorino disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ses épaules tombent un peu. Papa s'accroupit à la même hauteur. Tu vois Nina, Victorino ? Oui, papa. Tes mains sont collantes, Victorino ? Un peu, maman.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Kenzo arrive au parc avec papa. L'herbe sent la pluie. Zoé arrive aussi. Zoé a des lunettes. Zoé a les cheveux tressés. Zoé porte un gilet rouge. Kenzo regarde. Un petit rire commence. Papa parle tout de suite. Papa dit : on ne va &lt;emphasis&gt;pas&lt;/emphasis&gt; rire de l'apparence. Les lunettes aident à voir. Les cheveux sont les cheveux. L'habit tient chaud. On joue. Kenzo hoche la tête. Il va vers Zoé. Ils prennent la corde. Ils sautent. Parce qu'on ne va pas rire, le jeu continue. Papa dit encore : on ne va pas rire de l'apparence. Kenzo tend la corde. Zoé saute. Les lunettes restent sur le nez. Le gilet rouge bouge. Ils sourient. [pause]</t>
+          <t>Une goutte de résine colle au tronc. Elle fait un petit fil, chaud et collant. Ça colle, papa ! Tu la vois, sur l'écorce ? Oui, un petit fil. Le pin sent la résine, tout près. Sur l'écorce, un &lt;emphasis&gt;éclat de résine&lt;/emphasis&gt; brille. Il brille, maman. Tu le vois, le petit point ? Oui, un petit point. Une pomme de pin roule dans l'herbe. Elle fait toc, sec et rond. J'ai entendu le toc. La pomme de pin ? Oui, papa. L'écorce est rugueuse, sous la main. Elle pique un peu. Papa décroche la corde de la branche. Le coton est froid, un peu lourd. Le coton sent la pluie, Victorino ? Il est mouillé. En ce moment, Victorino tient un bout. Il veut cinq sauts, tout de suite. Je veux tourner, maintenant ! Nina saute cinq fois. Cinq fois, sans s'arrêter ? Oui, papa. On compte tout haut ? Oui, tout haut. Nina arrive sur le gravier. Le gravier fait criss-criss, sous ses pas. Nina a des lunettes. Nina a les cheveux tressés. Elle porte un gilet rouge. Nina, tu sautes au milieu ? Tu sautes, Nina ? Oui. Papa tient l'autre bout. Victorino regarde les lunettes, trop longtemps. Un rire commence dans sa bouche. Nina ne dit rien. Le sourire de Nina disparaît. Tu vas au milieu, maintenant ! Nina recule d'un pas. Non. Oh. Victorino tourne la corde trop vite, tout seul. La corde tape l'herbe, trop lourde. Ça fait un bruit mou. Un peu de terre colle au coton. Elle ne monte pas ! Elle est mouillée. L'éclat de résine tremble, puis tient. Le sourire de Victorino disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ses épaules tombent un peu. Papa s'accroupit à la même hauteur. Tu vois Nina, Victorino ? Oui, papa. Tes mains sont collantes, Victorino ? Un peu, maman. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1275,30 +1275,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>pas</t>
+          <t>éclat de résine</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1321,46 +1321,74 @@
       <c r="AU2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience puis découragement; intensite=2; destinataire=enfant; sous_texte=il_veut_cinq_sauts_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Une pomme de pin tombe dans l'herbe.
-narrateur|Elle fait un petit toc.
-narrateur|Le pin sent la résine.
-narrateur|L'écorce est rugueuse sous la main.
-narrateur|Un peu de sève brille au soleil.
-narrateur|Papa décroche la corde.
-narrateur|Le coton est encore froid.
-narrateur|Une fourmi monte sur l'écorce.
-papa|Tu as entendu le toc, Victorino ?
-enfant-m|La pomme de pin.
-papa|Oui.
-papa|Elle est tombée toute seule.
+          <t>narrateur|Une goutte de résine colle au tronc.
+narrateur|Elle fait un petit fil, chaud et collant.
+enfant-m|Ça colle, papa !
+papa|Tu la vois, sur l'écorce ?
+enfant-m|Oui, un petit fil.
+narrateur|Le pin sent la résine, tout près.
+narrateur|Sur l'écorce, un éclat de résine brille.
+enfant-m|Il brille, maman.
+maman|Tu le vois, le petit point ?
+enfant-m|Oui, un petit point.
+narrateur|Une pomme de pin roule dans l'herbe.
+narrateur|Elle fait toc, sec et rond.
+enfant-m|J'ai entendu le toc.
+papa|La pomme de pin ?
+enfant-m|Oui, papa.
+maman|L'écorce est rugueuse, sous la main.
+enfant-m|Elle pique un peu.
+narrateur|Papa décroche la corde de la branche.
+narrateur|Le coton est froid, un peu lourd.
+maman|Le coton sent la pluie, Victorino ?
+enfant-m|Il est mouillé.
 narrateur|En ce moment, Victorino tient un bout.
-narrateur|La corde sent le coton humide.
-enfant-m|Je veux tourner.
+narrateur|Il veut cinq sauts, tout de suite.
+enfant-m|Je veux tourner, maintenant !
 enfant-m|Nina saute cinq fois.
-papa|Cinq fois sans s'arrêter ?
-enfant-m|Oui.
-papa|On compte tout haut.
+papa|Cinq fois, sans s'arrêter ?
+enfant-m|Oui, papa.
+maman|On compte tout haut ?
+enfant-m|Oui, tout haut.
 narrateur|Nina arrive sur le gravier.
-narrateur|Le gravier fait criss-criss.
+narrateur|Le gravier fait criss-criss, sous ses pas.
 narrateur|Nina a des lunettes.
 narrateur|Nina a les cheveux tressés.
 narrateur|Elle porte un gilet rouge.
-papa|Nina, tu sautes au milieu.
+papa|Nina, tu sautes au milieu ?
 enfant-m|Tu sautes, Nina ?
 copine|Oui.
 narrateur|Papa tient l'autre bout.
-narrateur|La corde tourne.
-narrateur|Elle tape l'herbe, trop lourde.
+narrateur|Victorino regarde les lunettes, trop longtemps.
+narrateur|Un rire commence dans sa bouche.
+narrateur|Nina ne dit rien.
+narrateur|Le sourire de Nina disparaît.
+enfant-m|Tu vas au milieu, maintenant !
+narrateur|Nina recule d'un pas.
+copine|Non.
+enfant-m|Oh.
+narrateur|Victorino tourne la corde trop vite, tout seul.
+narrateur|La corde tape l'herbe, trop lourde.
 narrateur|Ça fait un bruit mou.
 narrateur|Un peu de terre colle au coton.
-enfant-m|Elle ne monte pas.
+enfant-m|Elle ne monte pas !
 copine|Elle est mouillée.
-papa|On peut l'essuyer.
-papa|Sur le tronc.
-papa|Puis on recompte.</t>
+narrateur|L'éclat de résine tremble, puis tient.
+narrateur|Le sourire de Victorino disparaît.
+narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.
+narrateur|Ses épaules tombent un peu.
+narrateur|Papa s'accroupit à la même hauteur.
+papa|Tu vois Nina, Victorino ?
+enfant-m|Oui, papa.
+maman|Tes mains sont collantes, Victorino ?
+enfant-m|Un peu, maman.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1397,12 +1425,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Nina a des lunettes. Que fait-on ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Nina a des &lt;emphasis level="moderate"&gt;lunettes&lt;/emphasis&gt;. Que fait-on ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Zoé a des lunettes. Que fait-on ?&lt;/slow&gt;</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Nina a des &lt;emphasis&gt;lunettes&lt;/emphasis&gt;. Que fait-on ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1412,7 +1440,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>jouer | ensemble | sauter | on joue | essuyer | pas rire</t>
+          <t>jouer | on joue | ensemble | sauter | pas rire | les cinq sauts</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1427,7 +1455,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>On saute ensemble. Que fait-on ?</t>
+          <t>On joue. Nina a des lunettes. Que fait-on ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1465,7 +1493,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1476,7 +1504,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1491,34 +1519,38 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="2" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>lunettes</t>
+        </is>
+      </c>
       <c r="AI3" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1533,17 +1565,17 @@
         <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=on_joue_nina_a_des_lunettes; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1576,17 +1608,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorino va vers Nina. Ils essuient la corde. Vous frottez le coton. Merci, Victorino. Merci, Nina. Le tronc sent la résine. Un peu de sève colle aux doigts. La corde redevient plus légère. Elle est moins lourde. On reprend ? On reprend. Nina suit la corde des yeux. On saute. Victorino tourne tout doux. La corde siffle un tout petit peu. Nina saute une fois. Un. Encore. Tu regardes la corde, Nina.</t>
+          <t>Victorino veut les cinq sauts, tout de suite. Je tourne, maintenant ! Il avance trop vite vers Nina. Les mots se bousculent dans sa bouche. Non. Nina reste un peu plus loin. Oh. Le sourire ne revient pas. Victorino refuse de foncer. Il referme la bouche. Personne ne parle. Il observe la corde, un instant. Il écoute le toc de la pomme de pin. Tu veux les cinq sauts avec Nina ? Papa reste à la même hauteur. Tu tiens le bout ? Nina ne dit rien, d'abord. Elle pose les mains sur le coton. Je le tiens. D'accord. Merci, Victorino. Papa a vu les deux, sous le pin. La résine colle un peu, sous les doigts. Elle est chaude. Ils essuient la corde sur le tronc. Nina tient le coton, plus près. La corde redevient plus légère, cette fois. Elle monte ! Oui. Tu la vois, la corde ? Oui, papa. Au milieu, Nina ? J'y vais. Victorino tourne, sans se presser. Nina suit la corde des yeux. Nina saute une fois. Un. Deux. Le ventre de Victorino se desserre. Les épaules se relèvent un peu. On reste sous le pin ? Oui. Tes mains sont au chaud ? Un peu, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Victorino va vers Nina. Ils essuient la corde. Vous frottez le coton. Merci, Victorino. Merci, Nina. Le tronc sent la résine. Un peu de sève colle aux doigts. La corde redevient plus légère. Elle est moins lourde. On reprend ? On reprend. Nina suit la corde des yeux. On saute. Victorino tourne tout doux. La corde siffle un tout petit peu. Nina saute une fois. Un. Encore. Tu regardes la corde, Nina.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Victorino veut les cinq sauts, tout de suite. Je tourne, maintenant ! Il avance trop vite vers Nina. Les mots se bousculent dans sa bouche. Non. Nina reste un peu plus loin. Oh. Le sourire ne revient pas. Victorino refuse de foncer. Il referme la bouche. Personne ne parle. Il observe la &lt;emphasis level="moderate"&gt;corde&lt;/emphasis&gt;, un instant. Il écoute le toc de la pomme de pin. Tu veux les cinq sauts avec Nina ? Papa reste à la même hauteur. Tu tiens le bout ? Nina ne dit rien, d'abord. Elle pose les mains sur le coton. Je le tiens. D'accord. Merci, Victorino. Papa a vu les deux, sous le pin. La résine colle un peu, sous les doigts. Elle est chaude. Ils essuient la corde sur le tronc. Nina tient le coton, plus près. La corde redevient plus légère, cette fois. Elle monte ! Oui. Tu la vois, la corde ? Oui, papa. Au milieu, Nina ? J'y vais. Victorino tourne, sans se presser. Nina suit la corde des yeux. Nina saute une fois. Un. Deux. Le ventre de Victorino se desserre. Les épaules se relèvent un peu. On reste sous le pin ? Oui. Tes mains sont au chaud ? Un peu, maman.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a entendu papa. On ne va &lt;emphasis&gt;pas&lt;/emphasis&gt; rire de l'apparence. Kenzo et Zoé ont joué. [pause]</t>
+          <t>Victorino veut les cinq sauts, tout de suite. Je tourne, maintenant ! Il avance trop vite vers Nina. Les mots se bousculent dans sa bouche. Non. Nina reste un peu plus loin. Oh. Le sourire ne revient pas. Victorino refuse de foncer. Il referme la bouche. Personne ne parle. Il observe la &lt;emphasis&gt;corde&lt;/emphasis&gt;, un instant. Il écoute le toc de la pomme de pin. Tu veux les cinq sauts avec Nina ? Papa reste à la même hauteur. Tu tiens le bout ? Nina ne dit rien, d'abord. Elle pose les mains sur le coton. Je le tiens. D'accord. Merci, Victorino. Papa a vu les deux, sous le pin. La résine colle un peu, sous les doigts. Elle est chaude. Ils essuient la corde sur le tronc. Nina tient le coton, plus près. La corde redevient plus légère, cette fois. Elle monte ! Oui. Tu la vois, la corde ? Oui, papa. Au milieu, Nina ? J'y vais. Victorino tourne, sans se presser. Nina suit la corde des yeux. Nina saute une fois. Un. Deux. Le ventre de Victorino se desserre. Les épaules se relèvent un peu. On reste sous le pin ? Oui. Tes mains sont au chaud ? Un peu, maman. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1633,7 +1665,7 @@
         </is>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
@@ -1641,10 +1673,10 @@
         </is>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1667,30 +1699,30 @@
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>pas</t>
+          <t>corde</t>
         </is>
       </c>
       <c r="AI4" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1699,10 +1731,10 @@
         </is>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AS4" s="2" t="n">
         <v>100</v>
@@ -1715,30 +1747,60 @@
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=résolution; intention=faire_vivre_le_geste; emotion=retenue puis fierté_calme; intensite=2; destinataire=enfant; sous_texte=ils_tiennent_la_corde_a_deux; tempo=naturel; sourire=léger; respiration=relâchée</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Victorino va vers Nina.
-narrateur|Ils essuient la corde.
-papa|Vous frottez le coton.
+          <t>narrateur|Victorino veut les cinq sauts, tout de suite.
+enfant-m|Je tourne, maintenant !
+narrateur|Il avance trop vite vers Nina.
+narrateur|Les mots se bousculent dans sa bouche.
+copine|Non.
+narrateur|Nina reste un peu plus loin.
+enfant-m|Oh.
+narrateur|Le sourire ne revient pas.
+narrateur|Victorino refuse de foncer.
+narrateur|Il referme la bouche.
+narrateur|Personne ne parle.
+narrateur|Il observe la corde, un instant.
+narrateur|Il écoute le toc de la pomme de pin.
+papa|Tu veux les cinq sauts avec Nina ?
+narrateur|Papa reste à la même hauteur.
+enfant-m|Tu tiens le bout ?
+narrateur|Nina ne dit rien, d'abord.
+narrateur|Elle pose les mains sur le coton.
+copine|Je le tiens.
+enfant-m|D'accord.
 papa|Merci, Victorino.
-papa|Merci, Nina.
-narrateur|Le tronc sent la résine.
-narrateur|Un peu de sève colle aux doigts.
-narrateur|La corde redevient plus légère.
-enfant-m|Elle est moins lourde.
-enfant-m|On reprend ?
-copine|On reprend.
-papa|Nina suit la corde des yeux.
-papa|On saute.
-narrateur|Victorino tourne tout doux.
-narrateur|La corde siffle un tout petit peu.
+narrateur|Papa a vu les deux, sous le pin.
+maman|La résine colle un peu, sous les doigts.
+enfant-m|Elle est chaude.
+narrateur|Ils essuient la corde sur le tronc.
+narrateur|Nina tient le coton, plus près.
+narrateur|La corde redevient plus légère, cette fois.
+enfant-m|Elle monte !
+copine|Oui.
+papa|Tu la vois, la corde ?
+enfant-m|Oui, papa.
+maman|Au milieu, Nina ?
+copine|J'y vais.
+narrateur|Victorino tourne, sans se presser.
+narrateur|Nina suit la corde des yeux.
 narrateur|Nina saute une fois.
 copine|Un.
-enfant-m|Encore.
-papa|Tu regardes la corde, Nina.</t>
+enfant-m|Deux.
+narrateur|Le ventre de Victorino se desserre.
+narrateur|Les épaules se relèvent un peu.
+papa|On reste sous le pin ?
+enfant-m|Oui.
+maman|Tes mains sont au chaud ?
+enfant-m|Un peu, maman.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>corde</t>
         </is>
       </c>
     </row>
@@ -1765,17 +1827,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nina saute encore. Deux. Trois. Quatre. Le gilet rouge bouge. Les tresses tapent le dos. Les lunettes restent bien. Cinq ! Cinq ! Bravo. Tu as tourné sans t'arrêter. La corde se pose dans l'herbe. On reverse les rôles ? À toi le milieu. Nina tourne à son tour. Victorino saute. Ses chaussures font toc. C'est plus facile. Oui. La corde est sèche. Un rayon passe entre les aiguilles. Il allume le gilet rouge. La fourmi est encore sur l'écorce. La pomme de pin reste dans l'herbe. On a eu nos cinq sauts. Oui. Cinq.</t>
+          <t>Nina saute, plus vite. Trois. Quatre. Le gilet rouge bouge. Les tresses tapent le dos. Les lunettes restent sur le nez. Cinq, maintenant ! Il tourne trop vite, tout de suite. Il regarde les lunettes, trop longtemps. Un rire revient dans sa bouche. Attends. Nina lâche le milieu. La corde penche vers l'herbe. Ça tombe ! Victorino avance les mains, trop vite. Puis il s'arrête net. Victorino refuse de foncer, cette fois. Ses mains se ferment, puis s'ouvrent. Personne ne dit la suite. Il observe la corde, un instant. Il écoute le toc de la pomme de pin. Sur l'écorce, un éclat de résine luit. Là, sur l'écorce. Tu sautes, Nina ? Nina ne dit rien. Elle reprend le milieu, sans parler. Oui. Victorino tourne, sans se presser. Nina saute. Cinq ! Cinq ! Tu as tourné sans t'arrêter ? Oui, papa. Le gilet est chaud, Nina ? Un peu. La corde se pose dans l'herbe. On reverse les rôles ? À toi le milieu. Nina tourne à son tour. Victorino saute. Ses chaussures font toc. C'est plus facile. La corde est sèche ? Oui, papa. Un rayon passe entre les aiguilles. Il allume le gilet.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Nina saute encore. Deux. Trois. Quatre. Le gilet rouge bouge. Les tresses tapent le dos. Les lunettes restent bien. Cinq ! Cinq ! Bravo. Tu as tourné sans t'arrêter. La corde se pose dans l'herbe. On reverse les rôles ? À toi le milieu. Nina tourne à son tour. Victorino saute. Ses chaussures font toc. C'est plus facile. Oui. La corde est sèche. Un rayon passe entre les aiguilles. Il allume le gilet rouge. La fourmi est encore sur l'écorce. La pomme de pin reste dans l'herbe. On a eu nos cinq sauts. Oui. Cinq.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nina saute, plus vite. Trois. Quatre. Le gilet rouge bouge. Les tresses tapent le dos. Les lunettes restent sur le nez. Cinq, maintenant ! Il tourne trop vite, tout de suite. Il regarde les lunettes, trop longtemps. Un rire revient dans sa bouche. Attends. Nina lâche le milieu. La corde penche vers l'herbe. Ça tombe ! Victorino avance les mains, trop vite. Puis il s'arrête net. Victorino refuse de foncer, cette fois. Ses mains se ferment, puis s'ouvrent. Personne ne dit la suite. Il observe la corde, un instant. Il écoute le toc de la pomme de pin. Sur l'écorce, un &lt;emphasis level="moderate"&gt;éclat de résine&lt;/emphasis&gt; luit. Là, sur l'écorce. Tu sautes, Nina ? Nina ne dit rien. Elle reprend le milieu, sans parler. Oui. Victorino tourne, sans se presser. Nina saute. Cinq ! Cinq ! Tu as tourné sans t'arrêter ? Oui, papa. Le gilet est chaud, Nina ? Un peu. La corde se pose dans l'herbe. On reverse les rôles ? À toi le milieu. Nina tourne à son tour. Victorino saute. Ses chaussures font toc. C'est plus facile. La corde est sèche ? Oui, papa. Un rayon passe entre les aiguilles. Il allume le gilet.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Kenzo pose la corde. Papa verse de l'eau. Merci, dit Zoé. [pause]</t>
+          <t>Nina saute, plus vite. Trois. Quatre. Le gilet rouge bouge. Les tresses tapent le dos. Les lunettes restent sur le nez. Cinq, maintenant ! Il tourne trop vite, tout de suite. Il regarde les lunettes, trop longtemps. Un rire revient dans sa bouche. Attends. Nina lâche le milieu. La corde penche vers l'herbe. Ça tombe ! Victorino avance les mains, trop vite. Puis il s'arrête net. Victorino refuse de foncer, cette fois. Ses mains se ferment, puis s'ouvrent. Personne ne dit la suite. Il observe la corde, un instant. Il écoute le toc de la pomme de pin. Sur l'écorce, un &lt;emphasis&gt;éclat de résine&lt;/emphasis&gt; luit. Là, sur l'écorce. Tu sautes, Nina ? Nina ne dit rien. Elle reprend le milieu, sans parler. Oui. Victorino tourne, sans se presser. Nina saute. Cinq ! Cinq ! Tu as tourné sans t'arrêter ? Oui, papa. Le gilet est chaud, Nina ? Un peu. La corde se pose dans l'herbe. On reverse les rôles ? À toi le milieu. Nina tourne à son tour. Victorino saute. Ses chaussures font toc. C'est plus facile. La corde est sèche ? Oui, papa. Un rayon passe entre les aiguilles. Il allume le gilet. [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1822,7 +1884,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1830,10 +1892,10 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1854,28 +1916,32 @@
       <c r="AG5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr">
+        <is>
+          <t>éclat de résine</t>
+        </is>
+      </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>lively</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.37</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1884,10 +1950,10 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
@@ -1898,20 +1964,48 @@
       <c r="AU5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=action; intention=entraîner; emotion=élan puis prudence; intensite=2; destinataire=enfant; sous_texte=il_refuse_de_foncer_retrouve_l_eclat; tempo=vif puis posé; sourire=léger; respiration=courte</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Nina saute encore.
-copine|Deux.
-enfant-m|Trois.
-copine|Quatre.
+          <t>narrateur|Nina saute, plus vite.
+copine|Trois.
+enfant-m|Quatre.
 narrateur|Le gilet rouge bouge.
 narrateur|Les tresses tapent le dos.
-narrateur|Les lunettes restent bien.
+narrateur|Les lunettes restent sur le nez.
+enfant-m|Cinq, maintenant !
+narrateur|Il tourne trop vite, tout de suite.
+narrateur|Il regarde les lunettes, trop longtemps.
+narrateur|Un rire revient dans sa bouche.
+copine|Attends.
+narrateur|Nina lâche le milieu.
+narrateur|La corde penche vers l'herbe.
+enfant-m|Ça tombe !
+narrateur|Victorino avance les mains, trop vite.
+narrateur|Puis il s'arrête net.
+narrateur|Victorino refuse de foncer, cette fois.
+narrateur|Ses mains se ferment, puis s'ouvrent.
+narrateur|Personne ne dit la suite.
+narrateur|Il observe la corde, un instant.
+narrateur|Il écoute le toc de la pomme de pin.
+narrateur|Sur l'écorce, un éclat de résine luit.
+enfant-m|Là, sur l'écorce.
+enfant-m|Tu sautes, Nina ?
+narrateur|Nina ne dit rien.
+narrateur|Elle reprend le milieu, sans parler.
+copine|Oui.
+narrateur|Victorino tourne, sans se presser.
+narrateur|Nina saute.
 copine|Cinq !
 enfant-m|Cinq !
-papa|Bravo.
-papa|Tu as tourné sans t'arrêter.
+papa|Tu as tourné sans t'arrêter ?
+enfant-m|Oui, papa.
+maman|Le gilet est chaud, Nina ?
+copine|Un peu.
 narrateur|La corde se pose dans l'herbe.
 papa|On reverse les rôles ?
 copine|À toi le milieu.
@@ -1919,15 +2013,15 @@
 narrateur|Victorino saute.
 narrateur|Ses chaussures font toc.
 enfant-m|C'est plus facile.
-papa|Oui.
-papa|La corde est sèche.
-narrateur|Un rayon passe entre les aiguilles.
-narrateur|Il allume le gilet rouge.
-narrateur|La fourmi est encore sur l'écorce.
-narrateur|La pomme de pin reste dans l'herbe.
-papa|On a eu nos cinq sauts.
-enfant-m|Oui.
-enfant-m|Cinq.</t>
+papa|La corde est sèche ?
+enfant-m|Oui, papa.
+maman|Un rayon passe entre les aiguilles.
+enfant-m|Il allume le gilet.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>corde</t>
         </is>
       </c>
     </row>
@@ -1954,17 +2048,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La corde pend à la branche. Elle n'est plus lourde. Nina a sauté cinq fois. Oui. Vous avez eu vos cinq sauts. Le pin sent encore la résine.</t>
+          <t>Ils restent sous le pin. Maman essuie un peu de terre. On a eu les cinq sauts, papa. Tu les as vus, toi ? Oui, au milieu. On est bien, ici. Victorino tapote la corde du doigt. Elle a une trace de résine. Tu la vois, la trace ? Oui, maman. La corde est restée, Victorino. Oui, avec Nina. La corde est restée. Ça sent la résine, un peu tiède. Et le pin, maman. Oui, dans l'air. La pomme de pin reste dans l'herbe. Un éclat de résine tient sur l'écorce.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>La corde pend à la branche. Elle n'est plus lourde. Nina a sauté cinq fois. Oui. Vous avez eu vos cinq sauts. Le pin sent encore la résine.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Ils restent sous le pin. Maman essuie un peu de terre. On a eu les cinq sauts, papa. Tu les as vus, toi ? Oui, au milieu. On est bien, ici. Victorino tapote la corde du doigt. Elle a une trace de résine. Tu la vois, la trace ? Oui, maman. La corde est restée, Victorino. Oui, avec Nina. La corde est restée. Ça sent la résine, un peu tiède. Et le pin, maman. Oui, dans l'air. La pomme de pin reste dans l'herbe. Un &lt;emphasis level="moderate"&gt;éclat de résine&lt;/emphasis&gt; tient sur l'écorce.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Ils restent sous le pin. Maman essuie un peu de terre. On a eu les cinq sauts, papa. Tu les as vus, toi ? Oui, au milieu. On est bien, ici. Victorino tapote la corde du doigt. Elle a une trace de résine. Tu la vois, la trace ? Oui, maman. La corde est restée, Victorino. Oui, avec Nina. La corde est restée. Ça sent la résine, un peu tiède. Et le pin, maman. Oui, dans l'air. La pomme de pin reste dans l'herbe. Un &lt;emphasis&gt;éclat de résine&lt;/emphasis&gt; tient sur l'écorce.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2011,18 +2105,18 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2031,12 +2125,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2045,17 +2139,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat de résine</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2064,11 +2162,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2077,29 +2175,50 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse_et_fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_eclat_du_debut_tient_sur_l_ecorce; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|La corde pend à la branche.
-narrateur|Elle n'est plus lourde.
-enfant-m|Nina a sauté cinq fois.
-papa|Oui.
-papa|Vous avez eu vos cinq sauts.
-narrateur|Le pin sent encore la résine.</t>
+          <t>narrateur|Ils restent sous le pin.
+narrateur|Maman essuie un peu de terre.
+enfant-m|On a eu les cinq sauts, papa.
+papa|Tu les as vus, toi ?
+enfant-m|Oui, au milieu.
+maman|On est bien, ici.
+narrateur|Victorino tapote la corde du doigt.
+enfant-m|Elle a une trace de résine.
+maman|Tu la vois, la trace ?
+enfant-m|Oui, maman.
+papa|La corde est restée, Victorino.
+enfant-m|Oui, avec Nina.
+copine|La corde est restée.
+narrateur|Ça sent la résine, un peu tiède.
+enfant-m|Et le pin, maman.
+maman|Oui, dans l'air.
+narrateur|La pomme de pin reste dans l'herbe.
+narrateur|Un éclat de résine tient sur l'écorce.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>pin</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2205,6 +2324,13 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
